--- a/SectionsFHIRCorps/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/SectionsFHIRCorps/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T10:31:15+00:00</t>
+    <t>2026-03-02T10:56:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SectionsFHIRCorps/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/SectionsFHIRCorps/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T10:56:24+00:00</t>
+    <t>2026-03-02T10:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SectionsFHIRCorps/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/SectionsFHIRCorps/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T10:53:58+00:00</t>
+    <t>2026-03-04T08:48:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SectionsFHIRCorps/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/SectionsFHIRCorps/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T08:48:36+00:00</t>
+    <t>2026-03-12T10:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
